--- a/db/DB_수사종결까지.xlsx
+++ b/db/DB_수사종결까지.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tthdd\Documents\로스쿨\변시\형법\형소\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\songjoo\Documents\GitHub\word-game\db\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DAAD36E-F758-484A-9276-6400FEE6C0E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D66877F8-1C33-48FB-8085-F28568F65329}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" firstSheet="1" activeTab="1" xr2:uid="{5A5E7394-FEFB-4E15-8D3D-4FA3946DC3B9}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="3" xr2:uid="{5A5E7394-FEFB-4E15-8D3D-4FA3946DC3B9}"/>
   </bookViews>
   <sheets>
     <sheet name="관할 및 제척기피" sheetId="1" r:id="rId1"/>
@@ -532,11 +532,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>인정신문 단계에서 밝혀진 경우 
-위장출석자 퇴정시키고 진정한 피고인 소환</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>사실심리/판결선고 단계에서 밝혀진 경우
 위장출석자에 대한 조치 : &lt;공소기각판결&gt;
 진정한 피고인에 대한 조치 : 소환하여 제1심 공판절차 진행</t>
@@ -900,10 +895,6 @@
   </si>
   <si>
     <t>소송능력 있으면 고소능력 인정되며, 민법상 &lt;행위능력&gt; 없는 자라도 피해를 받은 사실을 이해하고 고소에 따른 사회관계상 이해관계 알아차릴 수 있는 사실상 의사능력으로 충분하다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>부재자재산관리인은 법원으로부터 고소권행사에 관한 허가를 얻으면 적법한 고소권자에 해당한다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2263,11 +2254,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>공소제기 전
-구속영장실질심사 시 변호인은 지방법원 판사에게 제출된 구속영장청구서 및 그에 첨부된 고소, 고발장, 피의자의 진술을 기재한 서류와 피의자가 제출한 서류를 열람할 수 있다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>불복방법
 피고인 또는 변호인은 검사가 거부, 제한하는 경우 법원에 대하여 열람등사 등 허용신청할 수 있다. 법원의 열람등사 허용결정은 판결 전 소송절차에 관한 것으로서 항고할 수 없고, 결정 즉시 &lt;집행력&gt; 발생한다.
 검사가 위 결정을 지체없이 이행하지 아니하면 해당 서류 등에 대한 증거신청할 수 없다. 
@@ -2290,6 +2276,20 @@
   </si>
   <si>
     <t>검찰청이 보관하는 &lt;불기소결정서&gt;는 제272조에 기하여 법원이 공무소 등에 송부요구한 서류로서 변호인 등이 열람·지정에 의한 공개의 대상이 된다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공소제기 전
+&lt;구속영장실질심사&gt; 시 변호인은 지방법원 판사에게 제출된 구속영장청구서 및 그에 첨부된 고소, 고발장, 피의자의 진술을 기재한 서류와 피의자가 제출한 서류를 열람할 수 있다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;인정신문&gt; 단계에서 밝혀진 경우 
+위장출석자 퇴정시키고 진정한 피고인 소환</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;부재자재산관리인&gt;은 법원으로부터 고소권행사에 관한 허가를 얻으면 적법한 고소권자에 해당한다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3715,7 +3715,7 @@
         <v>12</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="79" spans="2:11" ht="51" x14ac:dyDescent="0.45">
@@ -3723,7 +3723,7 @@
         <v>12</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="82" spans="2:11" x14ac:dyDescent="0.45">
@@ -3949,22 +3949,22 @@
     </row>
     <row r="21" spans="2:11" ht="34" x14ac:dyDescent="0.45">
       <c r="C21" s="1" t="s">
-        <v>107</v>
+        <v>495</v>
       </c>
     </row>
     <row r="22" spans="2:11" ht="51" x14ac:dyDescent="0.45">
       <c r="C22" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="23" spans="2:11" ht="34" x14ac:dyDescent="0.45">
       <c r="C23" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="26" spans="2:11" x14ac:dyDescent="0.45">
       <c r="C26" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="27" spans="2:11" ht="34" x14ac:dyDescent="0.45">
@@ -3972,13 +3972,13 @@
         <v>5</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D27" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E27" s="1" t="s">
         <v>112</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>113</v>
       </c>
       <c r="K27">
         <v>1</v>
@@ -3989,13 +3989,13 @@
         <v>5</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D28" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E28" s="1" t="s">
         <v>112</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>113</v>
       </c>
       <c r="K28">
         <v>1</v>
@@ -4006,13 +4006,13 @@
         <v>5</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D29" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E29" s="1" t="s">
         <v>112</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>113</v>
       </c>
       <c r="K29">
         <v>1</v>
@@ -4023,7 +4023,7 @@
         <v>12</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="31" spans="2:11" ht="68" x14ac:dyDescent="0.45">
@@ -4031,13 +4031,13 @@
         <v>5</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D31" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E31" s="1" t="s">
         <v>112</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>113</v>
       </c>
       <c r="K31">
         <v>2</v>
@@ -4045,13 +4045,13 @@
     </row>
     <row r="32" spans="2:11" ht="34" x14ac:dyDescent="0.45">
       <c r="C32" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D32" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E32" s="1" t="s">
         <v>112</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>113</v>
       </c>
       <c r="K32">
         <v>2</v>
@@ -4062,13 +4062,13 @@
         <v>5</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D33" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E33" s="1" t="s">
         <v>119</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>120</v>
       </c>
       <c r="K33">
         <v>1</v>
@@ -4076,7 +4076,7 @@
     </row>
     <row r="36" spans="2:11" x14ac:dyDescent="0.45">
       <c r="C36" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="37" spans="2:11" ht="51" x14ac:dyDescent="0.45">
@@ -4084,7 +4084,7 @@
         <v>12</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="38" spans="2:11" ht="119" x14ac:dyDescent="0.45">
@@ -4092,7 +4092,7 @@
         <v>12</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="39" spans="2:11" ht="51" x14ac:dyDescent="0.45">
@@ -4100,12 +4100,12 @@
         <v>12</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="42" spans="2:11" x14ac:dyDescent="0.45">
       <c r="C42" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="43" spans="2:11" x14ac:dyDescent="0.45">
@@ -4113,7 +4113,7 @@
         <v>12</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="44" spans="2:11" x14ac:dyDescent="0.45">
@@ -4121,7 +4121,7 @@
         <v>12</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="45" spans="2:11" ht="68" x14ac:dyDescent="0.45">
@@ -4129,7 +4129,7 @@
         <v>12</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="46" spans="2:11" ht="51" x14ac:dyDescent="0.45">
@@ -4137,19 +4137,19 @@
         <v>5</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D46" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E46" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="E46" s="1" t="s">
+      <c r="F46" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="F46" s="1" t="s">
-        <v>133</v>
-      </c>
       <c r="G46" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="K46">
         <v>1</v>
@@ -4160,19 +4160,19 @@
         <v>5</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D47" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E47" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="E47" s="1" t="s">
+      <c r="F47" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="F47" s="1" t="s">
-        <v>133</v>
-      </c>
       <c r="G47" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="K47">
         <v>1</v>
@@ -4183,19 +4183,19 @@
         <v>5</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D48" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E48" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="E48" s="1" t="s">
+      <c r="F48" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="F48" s="1" t="s">
-        <v>133</v>
-      </c>
       <c r="G48" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="K48">
         <v>1</v>
@@ -4206,19 +4206,19 @@
         <v>5</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D49" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E49" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="E49" s="1" t="s">
+      <c r="F49" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="F49" s="1" t="s">
-        <v>133</v>
-      </c>
       <c r="G49" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="K49">
         <v>1</v>
@@ -4229,19 +4229,19 @@
         <v>5</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D50" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E50" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="E50" s="1" t="s">
+      <c r="F50" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="F50" s="1" t="s">
-        <v>133</v>
-      </c>
       <c r="G50" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="K50">
         <v>2</v>
@@ -4252,19 +4252,19 @@
         <v>5</v>
       </c>
       <c r="C51" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="D51" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="D51" s="1" t="s">
+      <c r="E51" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="E51" s="1" t="s">
+      <c r="F51" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="F51" s="1" t="s">
-        <v>133</v>
-      </c>
       <c r="G51" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="K51">
         <v>3</v>
@@ -4275,19 +4275,19 @@
         <v>5</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D52" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E52" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="E52" s="1" t="s">
+      <c r="F52" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="F52" s="1" t="s">
-        <v>133</v>
-      </c>
       <c r="G52" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="K52">
         <v>3</v>
@@ -4298,19 +4298,19 @@
         <v>5</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D53" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E53" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="E53" s="1" t="s">
+      <c r="F53" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="F53" s="1" t="s">
-        <v>133</v>
-      </c>
       <c r="G53" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="K53">
         <v>3</v>
@@ -4321,19 +4321,19 @@
         <v>5</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D54" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E54" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="E54" s="1" t="s">
+      <c r="F54" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="F54" s="1" t="s">
-        <v>133</v>
-      </c>
       <c r="G54" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="K54">
         <v>3</v>
@@ -4344,19 +4344,19 @@
         <v>5</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D55" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E55" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="E55" s="1" t="s">
+      <c r="F55" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="F55" s="1" t="s">
-        <v>133</v>
-      </c>
       <c r="G55" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="K55">
         <v>3</v>
@@ -4367,19 +4367,19 @@
         <v>5</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D56" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E56" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="E56" s="1" t="s">
+      <c r="F56" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="F56" s="1" t="s">
-        <v>133</v>
-      </c>
       <c r="G56" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="K56">
         <v>3</v>
@@ -4390,19 +4390,19 @@
         <v>5</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D57" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E57" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="E57" s="1" t="s">
+      <c r="F57" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="F57" s="1" t="s">
-        <v>133</v>
-      </c>
       <c r="G57" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="K57">
         <v>4</v>
@@ -4413,19 +4413,19 @@
         <v>5</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D58" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E58" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="E58" s="1" t="s">
+      <c r="F58" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="F58" s="1" t="s">
-        <v>133</v>
-      </c>
       <c r="G58" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="K58">
         <v>4</v>
@@ -4436,19 +4436,19 @@
         <v>5</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D59" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E59" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="E59" s="1" t="s">
+      <c r="F59" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="F59" s="1" t="s">
-        <v>133</v>
-      </c>
       <c r="G59" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="K59">
         <v>4</v>
@@ -4459,19 +4459,19 @@
         <v>5</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D60" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E60" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="E60" s="1" t="s">
+      <c r="F60" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="F60" s="1" t="s">
-        <v>133</v>
-      </c>
       <c r="G60" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="K60">
         <v>4</v>
@@ -4482,19 +4482,19 @@
         <v>5</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D61" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E61" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="E61" s="1" t="s">
+      <c r="F61" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="F61" s="1" t="s">
-        <v>133</v>
-      </c>
       <c r="G61" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="K61">
         <v>4</v>
@@ -4505,19 +4505,19 @@
         <v>5</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D62" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E62" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="E62" s="1" t="s">
+      <c r="F62" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="F62" s="1" t="s">
-        <v>133</v>
-      </c>
       <c r="G62" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="K62">
         <v>4</v>
@@ -4528,7 +4528,7 @@
         <v>12</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="64" spans="2:11" ht="85" x14ac:dyDescent="0.45">
@@ -4536,7 +4536,7 @@
         <v>12</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="65" spans="2:3" ht="68" x14ac:dyDescent="0.45">
@@ -4544,12 +4544,12 @@
         <v>12</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="68" spans="2:3" x14ac:dyDescent="0.45">
       <c r="C68" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="69" spans="2:3" ht="51" x14ac:dyDescent="0.45">
@@ -4557,7 +4557,7 @@
         <v>12</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="70" spans="2:3" ht="34" x14ac:dyDescent="0.45">
@@ -4565,7 +4565,7 @@
         <v>12</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="71" spans="2:3" ht="34" x14ac:dyDescent="0.45">
@@ -4573,7 +4573,7 @@
         <v>12</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="72" spans="2:3" ht="34" x14ac:dyDescent="0.45">
@@ -4581,17 +4581,17 @@
         <v>12</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="73" spans="2:3" ht="102" x14ac:dyDescent="0.45">
       <c r="C73" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="77" spans="2:3" x14ac:dyDescent="0.45">
       <c r="C77" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="78" spans="2:3" ht="68" x14ac:dyDescent="0.45">
@@ -4599,7 +4599,7 @@
         <v>12</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="79" spans="2:3" ht="34" x14ac:dyDescent="0.45">
@@ -4607,7 +4607,7 @@
         <v>11</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="80" spans="2:3" ht="34" x14ac:dyDescent="0.45">
@@ -4615,7 +4615,7 @@
         <v>11</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="81" spans="2:11" ht="51" x14ac:dyDescent="0.45">
@@ -4623,7 +4623,7 @@
         <v>11</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="82" spans="2:11" ht="85" x14ac:dyDescent="0.45">
@@ -4631,13 +4631,13 @@
         <v>5</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D82" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="E82" s="1" t="s">
         <v>164</v>
-      </c>
-      <c r="E82" s="1" t="s">
-        <v>165</v>
       </c>
       <c r="K82">
         <v>1</v>
@@ -4648,13 +4648,13 @@
         <v>5</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D83" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="E83" s="1" t="s">
         <v>164</v>
-      </c>
-      <c r="E83" s="1" t="s">
-        <v>165</v>
       </c>
       <c r="K83">
         <v>2</v>
@@ -4665,13 +4665,13 @@
         <v>5</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D84" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="E84" s="1" t="s">
         <v>164</v>
-      </c>
-      <c r="E84" s="1" t="s">
-        <v>165</v>
       </c>
       <c r="K84">
         <v>2</v>
@@ -4682,13 +4682,13 @@
         <v>5</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D85" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="E85" s="1" t="s">
         <v>164</v>
-      </c>
-      <c r="E85" s="1" t="s">
-        <v>165</v>
       </c>
       <c r="K85">
         <v>2</v>
@@ -4699,7 +4699,7 @@
         <v>12</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="87" spans="2:11" ht="85" x14ac:dyDescent="0.45">
@@ -4707,32 +4707,32 @@
         <v>12</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="90" spans="2:11" x14ac:dyDescent="0.45">
       <c r="C90" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
     </row>
     <row r="91" spans="2:11" ht="68" x14ac:dyDescent="0.45">
       <c r="C91" s="1" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="92" spans="2:11" ht="323" x14ac:dyDescent="0.45">
       <c r="C92" s="1" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
     </row>
     <row r="93" spans="2:11" ht="170" x14ac:dyDescent="0.45">
       <c r="C93" s="1" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
     </row>
     <row r="94" spans="2:11" ht="51" x14ac:dyDescent="0.45">
       <c r="C94" s="1" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
     </row>
   </sheetData>
@@ -4775,7 +4775,7 @@
     </row>
     <row r="3" spans="2:11" x14ac:dyDescent="0.45">
       <c r="C3" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="4" spans="2:11" ht="51" x14ac:dyDescent="0.45">
@@ -4783,12 +4783,12 @@
         <v>12</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="7" spans="2:11" x14ac:dyDescent="0.45">
       <c r="C7" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="8" spans="2:11" ht="34" x14ac:dyDescent="0.45">
@@ -4796,7 +4796,7 @@
         <v>12</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="9" spans="2:11" ht="34" x14ac:dyDescent="0.45">
@@ -4804,12 +4804,12 @@
         <v>12</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.45">
       <c r="C11" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="12" spans="2:11" ht="51" x14ac:dyDescent="0.45">
@@ -4817,12 +4817,12 @@
         <v>12</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.45">
       <c r="C15" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="16" spans="2:11" ht="85" x14ac:dyDescent="0.45">
@@ -4830,7 +4830,7 @@
         <v>12</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
   </sheetData>
@@ -4875,7 +4875,7 @@
     </row>
     <row r="3" spans="2:11" x14ac:dyDescent="0.45">
       <c r="C3" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="4" spans="2:11" ht="68" x14ac:dyDescent="0.45">
@@ -4883,7 +4883,7 @@
         <v>12</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="5" spans="2:11" ht="68" x14ac:dyDescent="0.45">
@@ -4891,7 +4891,7 @@
         <v>12</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.45">
@@ -4899,7 +4899,7 @@
         <v>12</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="7" spans="2:11" ht="51" x14ac:dyDescent="0.45">
@@ -4907,13 +4907,13 @@
         <v>5</v>
       </c>
       <c r="C7" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>226</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>228</v>
       </c>
       <c r="K7">
         <v>1</v>
@@ -4924,13 +4924,13 @@
         <v>5</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="K8">
         <v>1</v>
@@ -4941,13 +4941,13 @@
         <v>5</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="K9">
         <v>2</v>
@@ -4958,13 +4958,13 @@
         <v>5</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="K10">
         <v>2</v>
@@ -4975,13 +4975,13 @@
         <v>5</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="K11">
         <v>2</v>
@@ -4992,13 +4992,13 @@
         <v>5</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="K12">
         <v>2</v>
@@ -5009,13 +5009,13 @@
         <v>5</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="K13">
         <v>2</v>
@@ -5026,13 +5026,13 @@
         <v>5</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="K14">
         <v>2</v>
@@ -5043,13 +5043,13 @@
         <v>5</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="K15">
         <v>2</v>
@@ -5060,13 +5060,13 @@
         <v>5</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="K16">
         <v>1</v>
@@ -5077,13 +5077,13 @@
         <v>5</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="K17">
         <v>2</v>
@@ -5094,13 +5094,13 @@
         <v>5</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="K18">
         <v>1</v>
@@ -5111,13 +5111,13 @@
         <v>5</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="K19">
         <v>2</v>
@@ -5128,13 +5128,13 @@
         <v>5</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="K20">
         <v>1</v>
@@ -5145,13 +5145,13 @@
         <v>5</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="K21">
         <v>2</v>
@@ -5162,13 +5162,13 @@
         <v>5</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="K22">
         <v>2</v>
@@ -5179,13 +5179,13 @@
         <v>5</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="K23">
         <v>1</v>
@@ -5196,13 +5196,13 @@
         <v>5</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="K24">
         <v>2</v>
@@ -5213,19 +5213,19 @@
         <v>5</v>
       </c>
       <c r="C25" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="F25" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="D25" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>249</v>
-      </c>
       <c r="G25" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="K25">
         <v>1</v>
@@ -5236,19 +5236,19 @@
         <v>5</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="K26">
         <v>2</v>
@@ -5256,7 +5256,7 @@
     </row>
     <row r="29" spans="2:11" x14ac:dyDescent="0.45">
       <c r="C29" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="30" spans="2:11" ht="85" x14ac:dyDescent="0.45">
@@ -5264,7 +5264,7 @@
         <v>12</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="31" spans="2:11" ht="51" x14ac:dyDescent="0.45">
@@ -5272,7 +5272,7 @@
         <v>12</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="32" spans="2:11" ht="51" x14ac:dyDescent="0.45">
@@ -5280,7 +5280,7 @@
         <v>12</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="33" spans="2:3" ht="34" x14ac:dyDescent="0.45">
@@ -5288,12 +5288,12 @@
         <v>12</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.45">
       <c r="C36" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="37" spans="2:3" ht="51" x14ac:dyDescent="0.45">
@@ -5301,7 +5301,7 @@
         <v>12</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="38" spans="2:3" ht="51" x14ac:dyDescent="0.45">
@@ -5309,7 +5309,7 @@
         <v>12</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="39" spans="2:3" ht="34" x14ac:dyDescent="0.45">
@@ -5317,7 +5317,7 @@
         <v>12</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="40" spans="2:3" ht="34" x14ac:dyDescent="0.45">
@@ -5325,7 +5325,7 @@
         <v>12</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>196</v>
+        <v>496</v>
       </c>
     </row>
     <row r="41" spans="2:3" ht="68" x14ac:dyDescent="0.45">
@@ -5333,12 +5333,12 @@
         <v>12</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="44" spans="2:3" x14ac:dyDescent="0.45">
       <c r="C44" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="45" spans="2:3" ht="68" x14ac:dyDescent="0.45">
@@ -5346,7 +5346,7 @@
         <v>12</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="46" spans="2:3" ht="68" x14ac:dyDescent="0.45">
@@ -5354,12 +5354,12 @@
         <v>12</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="49" spans="2:11" x14ac:dyDescent="0.45">
       <c r="C49" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="50" spans="2:11" ht="34" x14ac:dyDescent="0.45">
@@ -5367,13 +5367,13 @@
         <v>5</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="K50">
         <v>1</v>
@@ -5384,13 +5384,13 @@
         <v>5</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="K51">
         <v>2</v>
@@ -5401,13 +5401,13 @@
         <v>5</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="K52">
         <v>2</v>
@@ -5418,13 +5418,13 @@
         <v>5</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="K53">
         <v>2</v>
@@ -5435,13 +5435,13 @@
         <v>5</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="K54">
         <v>2</v>
@@ -5452,13 +5452,13 @@
         <v>5</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="K55">
         <v>1</v>
@@ -5469,13 +5469,13 @@
         <v>5</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="K56">
         <v>2</v>
@@ -5486,13 +5486,13 @@
         <v>5</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="K57">
         <v>2</v>
@@ -5503,7 +5503,7 @@
         <v>12</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="59" spans="2:11" ht="34" x14ac:dyDescent="0.45">
@@ -5511,7 +5511,7 @@
         <v>12</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="60" spans="2:11" ht="34" x14ac:dyDescent="0.45">
@@ -5519,12 +5519,12 @@
         <v>12</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="63" spans="2:11" x14ac:dyDescent="0.45">
       <c r="C63" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="64" spans="2:11" ht="34" x14ac:dyDescent="0.45">
@@ -5532,7 +5532,7 @@
         <v>12</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="65" spans="2:3" ht="51" x14ac:dyDescent="0.45">
@@ -5540,7 +5540,7 @@
         <v>12</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="66" spans="2:3" ht="34" x14ac:dyDescent="0.45">
@@ -5548,7 +5548,7 @@
         <v>12</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="67" spans="2:3" ht="51" x14ac:dyDescent="0.45">
@@ -5556,7 +5556,7 @@
         <v>12</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="68" spans="2:3" ht="34" x14ac:dyDescent="0.45">
@@ -5564,7 +5564,7 @@
         <v>12</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="69" spans="2:3" ht="34" x14ac:dyDescent="0.45">
@@ -5572,7 +5572,7 @@
         <v>12</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="70" spans="2:3" ht="34" x14ac:dyDescent="0.45">
@@ -5580,7 +5580,7 @@
         <v>12</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="71" spans="2:3" ht="34" x14ac:dyDescent="0.45">
@@ -5588,7 +5588,7 @@
         <v>12</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="72" spans="2:3" ht="85" x14ac:dyDescent="0.45">
@@ -5596,12 +5596,12 @@
         <v>12</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="75" spans="2:3" x14ac:dyDescent="0.45">
       <c r="C75" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="76" spans="2:3" ht="34" x14ac:dyDescent="0.45">
@@ -5609,7 +5609,7 @@
         <v>12</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="77" spans="2:3" ht="68" x14ac:dyDescent="0.45">
@@ -5617,7 +5617,7 @@
         <v>12</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="78" spans="2:3" ht="51" x14ac:dyDescent="0.45">
@@ -5625,7 +5625,7 @@
         <v>12</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="79" spans="2:3" ht="34" x14ac:dyDescent="0.45">
@@ -5633,12 +5633,12 @@
         <v>12</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="82" spans="2:11" x14ac:dyDescent="0.45">
       <c r="C82" s="2" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="83" spans="2:11" ht="34" x14ac:dyDescent="0.45">
@@ -5646,7 +5646,7 @@
         <v>12</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="84" spans="2:11" ht="34" x14ac:dyDescent="0.45">
@@ -5654,7 +5654,7 @@
         <v>12</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="85" spans="2:11" x14ac:dyDescent="0.45">
@@ -5662,7 +5662,7 @@
         <v>12</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="86" spans="2:11" ht="34" x14ac:dyDescent="0.45">
@@ -5670,7 +5670,7 @@
         <v>12</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="87" spans="2:11" ht="51" x14ac:dyDescent="0.45">
@@ -5678,7 +5678,7 @@
         <v>12</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="88" spans="2:11" ht="34" x14ac:dyDescent="0.45">
@@ -5686,7 +5686,7 @@
         <v>12</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="89" spans="2:11" ht="34" x14ac:dyDescent="0.45">
@@ -5694,7 +5694,7 @@
         <v>12</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="90" spans="2:11" ht="68" x14ac:dyDescent="0.45">
@@ -5702,13 +5702,13 @@
         <v>5</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="K90">
         <v>1</v>
@@ -5719,7 +5719,7 @@
         <v>12</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
   </sheetData>
@@ -5764,7 +5764,7 @@
     </row>
     <row r="3" spans="2:11" x14ac:dyDescent="0.45">
       <c r="C3" s="2" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="4" spans="2:11" ht="170" x14ac:dyDescent="0.45">
@@ -5772,7 +5772,7 @@
         <v>12</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="5" spans="2:11" ht="102" x14ac:dyDescent="0.45">
@@ -5780,7 +5780,7 @@
         <v>12</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="6" spans="2:11" ht="34" x14ac:dyDescent="0.45">
@@ -5788,13 +5788,13 @@
         <v>5</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="K6">
         <v>2</v>
@@ -5805,13 +5805,13 @@
         <v>5</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="K7">
         <v>1</v>
@@ -5822,13 +5822,13 @@
         <v>5</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="K8">
         <v>1</v>
@@ -5839,13 +5839,13 @@
         <v>5</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="K9">
         <v>2</v>
@@ -5856,13 +5856,13 @@
         <v>5</v>
       </c>
       <c r="C10" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>271</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>273</v>
       </c>
       <c r="K10">
         <v>1</v>
@@ -5873,13 +5873,13 @@
         <v>5</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="K11">
         <v>1</v>
@@ -5890,13 +5890,13 @@
         <v>5</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="K12">
         <v>1</v>
@@ -5907,13 +5907,13 @@
         <v>5</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="K13">
         <v>2</v>
@@ -5924,13 +5924,13 @@
         <v>5</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="K14">
         <v>1</v>
@@ -5941,13 +5941,13 @@
         <v>5</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="K15">
         <v>2</v>
@@ -5955,7 +5955,7 @@
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.45">
       <c r="C18" s="2" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="19" spans="2:11" ht="51" x14ac:dyDescent="0.45">
@@ -5963,7 +5963,7 @@
         <v>12</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="20" spans="2:11" ht="34" x14ac:dyDescent="0.45">
@@ -5971,42 +5971,42 @@
         <v>12</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="21" spans="2:11" ht="102" x14ac:dyDescent="0.45">
       <c r="C21" s="1" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
     </row>
     <row r="22" spans="2:11" ht="85" x14ac:dyDescent="0.45">
       <c r="C22" s="1" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
     </row>
     <row r="23" spans="2:11" ht="119" x14ac:dyDescent="0.45">
       <c r="C23" s="1" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="24" spans="2:11" ht="34" x14ac:dyDescent="0.45">
       <c r="C24" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="25" spans="2:11" ht="68" x14ac:dyDescent="0.45">
       <c r="C25" s="1" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
     </row>
     <row r="26" spans="2:11" ht="85" x14ac:dyDescent="0.45">
       <c r="C26" s="1" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="29" spans="2:11" x14ac:dyDescent="0.45">
       <c r="C29" s="2" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="30" spans="2:11" ht="85" x14ac:dyDescent="0.45">
@@ -6014,7 +6014,7 @@
         <v>12</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="31" spans="2:11" ht="68" x14ac:dyDescent="0.45">
@@ -6022,7 +6022,7 @@
         <v>12</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="32" spans="2:11" ht="51" x14ac:dyDescent="0.45">
@@ -6030,13 +6030,13 @@
         <v>5</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="K32">
         <v>2</v>
@@ -6047,13 +6047,13 @@
         <v>5</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="K33">
         <v>2</v>
@@ -6061,7 +6061,7 @@
     </row>
     <row r="36" spans="2:11" x14ac:dyDescent="0.45">
       <c r="C36" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="37" spans="2:11" ht="221" x14ac:dyDescent="0.45">
@@ -6069,7 +6069,7 @@
         <v>12</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="38" spans="2:11" x14ac:dyDescent="0.45">
@@ -6077,7 +6077,7 @@
         <v>12</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
   </sheetData>
@@ -6122,38 +6122,38 @@
     </row>
     <row r="3" spans="2:11" x14ac:dyDescent="0.45">
       <c r="C3" s="2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="4" spans="2:11" ht="85" x14ac:dyDescent="0.45">
       <c r="C4" s="1" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="5" spans="2:11" ht="102" x14ac:dyDescent="0.45">
       <c r="C5" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="6" spans="2:11" ht="85" x14ac:dyDescent="0.45">
       <c r="C6" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="7" spans="2:11" ht="170" x14ac:dyDescent="0.45">
       <c r="C7" s="1" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="8" spans="2:11" ht="119" x14ac:dyDescent="0.45">
       <c r="C8" s="1" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="K8">
         <v>1</v>
@@ -6161,13 +6161,13 @@
     </row>
     <row r="9" spans="2:11" ht="119" x14ac:dyDescent="0.45">
       <c r="C9" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>297</v>
-      </c>
       <c r="E9" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="K9">
         <v>2</v>
@@ -6175,7 +6175,7 @@
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.45">
       <c r="C12" s="2" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="13" spans="2:11" ht="85" x14ac:dyDescent="0.45">
@@ -6183,7 +6183,7 @@
         <v>12</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="14" spans="2:11" ht="170" x14ac:dyDescent="0.45">
@@ -6191,7 +6191,7 @@
         <v>12</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="15" spans="2:11" ht="153" x14ac:dyDescent="0.45">
@@ -6199,7 +6199,7 @@
         <v>12</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="16" spans="2:11" ht="51" x14ac:dyDescent="0.45">
@@ -6207,19 +6207,19 @@
         <v>5</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="K16">
         <v>4</v>
@@ -6230,19 +6230,19 @@
         <v>4</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="K17">
         <v>4</v>
@@ -6253,19 +6253,19 @@
         <v>4</v>
       </c>
       <c r="C18" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="F18" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="D18" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>308</v>
-      </c>
       <c r="G18" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="K18">
         <v>2</v>
@@ -6276,19 +6276,19 @@
         <v>4</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="K19">
         <v>4</v>
@@ -6299,19 +6299,19 @@
         <v>4</v>
       </c>
       <c r="C20" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="E20" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="D20" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>311</v>
-      </c>
       <c r="F20" s="1" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="K20">
         <v>3</v>
@@ -6319,36 +6319,36 @@
     </row>
     <row r="23" spans="2:11" x14ac:dyDescent="0.45">
       <c r="C23" s="2" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="24" spans="2:11" ht="85" x14ac:dyDescent="0.45">
       <c r="C24" s="1" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="25" spans="2:11" ht="102" x14ac:dyDescent="0.45">
       <c r="C25" s="1" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="26" spans="2:11" ht="136" x14ac:dyDescent="0.45">
       <c r="C26" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="27" spans="2:11" ht="119" x14ac:dyDescent="0.45">
       <c r="C27" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="K27">
         <v>3</v>
@@ -6356,16 +6356,16 @@
     </row>
     <row r="28" spans="2:11" ht="68" x14ac:dyDescent="0.45">
       <c r="C28" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="K28">
         <v>3</v>
@@ -6373,16 +6373,16 @@
     </row>
     <row r="29" spans="2:11" ht="51" x14ac:dyDescent="0.45">
       <c r="C29" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="K29">
         <v>3</v>
@@ -6390,16 +6390,16 @@
     </row>
     <row r="30" spans="2:11" ht="68" x14ac:dyDescent="0.45">
       <c r="C30" s="1" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="K30">
         <v>3</v>
@@ -6407,81 +6407,81 @@
     </row>
     <row r="33" spans="3:11" x14ac:dyDescent="0.45">
       <c r="C33" s="2" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="34" spans="3:11" ht="68" x14ac:dyDescent="0.45">
       <c r="C34" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="35" spans="3:11" ht="34" x14ac:dyDescent="0.45">
       <c r="C35" s="4" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="36" spans="3:11" x14ac:dyDescent="0.45">
       <c r="C36" s="1" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="39" spans="3:11" x14ac:dyDescent="0.45">
       <c r="C39" s="2" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="40" spans="3:11" ht="68" x14ac:dyDescent="0.45">
       <c r="C40" s="1" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="41" spans="3:11" ht="204" x14ac:dyDescent="0.45">
       <c r="C41" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="42" spans="3:11" ht="68" x14ac:dyDescent="0.45">
       <c r="C42" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="43" spans="3:11" ht="102" x14ac:dyDescent="0.45">
       <c r="C43" s="1" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="44" spans="3:11" ht="85" x14ac:dyDescent="0.45">
       <c r="C44" s="1" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="45" spans="3:11" ht="68" x14ac:dyDescent="0.45">
       <c r="C45" s="1" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="46" spans="3:11" ht="153" x14ac:dyDescent="0.45">
       <c r="C46" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="47" spans="3:11" ht="153" x14ac:dyDescent="0.45">
       <c r="C47" s="1" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="48" spans="3:11" ht="34" x14ac:dyDescent="0.45">
       <c r="C48" s="1" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="K48">
         <v>1</v>
@@ -6489,16 +6489,16 @@
     </row>
     <row r="49" spans="3:11" ht="34" x14ac:dyDescent="0.45">
       <c r="C49" s="1" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="K49">
         <v>3</v>
@@ -6506,16 +6506,16 @@
     </row>
     <row r="50" spans="3:11" ht="34" x14ac:dyDescent="0.45">
       <c r="C50" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="E50" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="D50" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="E50" s="1" t="s">
-        <v>346</v>
-      </c>
       <c r="F50" s="1" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="K50">
         <v>3</v>
@@ -6523,16 +6523,16 @@
     </row>
     <row r="51" spans="3:11" ht="34" x14ac:dyDescent="0.45">
       <c r="C51" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="K51">
         <v>3</v>
@@ -6540,16 +6540,16 @@
     </row>
     <row r="52" spans="3:11" ht="34" x14ac:dyDescent="0.45">
       <c r="C52" s="1" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="K52">
         <v>3</v>
@@ -6557,16 +6557,16 @@
     </row>
     <row r="53" spans="3:11" ht="34" x14ac:dyDescent="0.45">
       <c r="C53" s="1" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="K53">
         <v>1</v>
@@ -6574,13 +6574,13 @@
     </row>
     <row r="54" spans="3:11" ht="68" x14ac:dyDescent="0.45">
       <c r="C54" s="1" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="K54">
         <v>2</v>
@@ -6588,13 +6588,13 @@
     </row>
     <row r="55" spans="3:11" ht="68" x14ac:dyDescent="0.45">
       <c r="C55" s="1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="K55">
         <v>1</v>
@@ -6602,13 +6602,13 @@
     </row>
     <row r="56" spans="3:11" ht="68" x14ac:dyDescent="0.45">
       <c r="C56" s="1" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="K56">
         <v>2</v>
@@ -6616,13 +6616,13 @@
     </row>
     <row r="57" spans="3:11" ht="68" x14ac:dyDescent="0.45">
       <c r="C57" s="1" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="K57">
         <v>1</v>
@@ -6630,63 +6630,63 @@
     </row>
     <row r="60" spans="3:11" x14ac:dyDescent="0.45">
       <c r="C60" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="61" spans="3:11" ht="102" x14ac:dyDescent="0.45">
       <c r="C61" s="1" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="64" spans="3:11" x14ac:dyDescent="0.45">
       <c r="C64" s="2" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="65" spans="3:11" ht="102" x14ac:dyDescent="0.45">
       <c r="C65" s="1" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="66" spans="3:11" ht="119" x14ac:dyDescent="0.45">
       <c r="C66" s="1" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="67" spans="3:11" ht="136" x14ac:dyDescent="0.45">
       <c r="C67" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="68" spans="3:11" ht="187" x14ac:dyDescent="0.45">
       <c r="C68" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
     </row>
     <row r="69" spans="3:11" ht="136" x14ac:dyDescent="0.45">
       <c r="C69" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="70" spans="3:11" ht="153" x14ac:dyDescent="0.45">
       <c r="C70" s="1" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="71" spans="3:11" ht="204" x14ac:dyDescent="0.45">
       <c r="C71" s="1" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="72" spans="3:11" ht="34" x14ac:dyDescent="0.45">
       <c r="C72" s="1" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="K72">
         <v>2</v>
@@ -6694,13 +6694,13 @@
     </row>
     <row r="73" spans="3:11" ht="34" x14ac:dyDescent="0.45">
       <c r="C73" s="1" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="K73">
         <v>1</v>
@@ -6708,13 +6708,13 @@
     </row>
     <row r="74" spans="3:11" ht="34" x14ac:dyDescent="0.45">
       <c r="C74" s="1" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="K74">
         <v>1</v>
@@ -6722,13 +6722,13 @@
     </row>
     <row r="75" spans="3:11" ht="34" x14ac:dyDescent="0.45">
       <c r="C75" s="1" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="K75">
         <v>2</v>
@@ -6736,17 +6736,17 @@
     </row>
     <row r="78" spans="3:11" x14ac:dyDescent="0.45">
       <c r="C78" s="2" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="79" spans="3:11" ht="136" x14ac:dyDescent="0.45">
       <c r="C79" s="1" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="80" spans="3:11" ht="34" x14ac:dyDescent="0.45">
       <c r="C80" s="1" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
   </sheetData>
@@ -6791,63 +6791,63 @@
     </row>
     <row r="3" spans="3:11" x14ac:dyDescent="0.45">
       <c r="C3" s="2" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="4" spans="3:11" ht="221" x14ac:dyDescent="0.45">
       <c r="C4" s="1" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="5" spans="3:11" ht="119" x14ac:dyDescent="0.45">
       <c r="C5" s="1" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="6" spans="3:11" ht="51" x14ac:dyDescent="0.45">
       <c r="C6" s="6" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="9" spans="3:11" x14ac:dyDescent="0.45">
       <c r="C9" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="10" spans="3:11" ht="85" x14ac:dyDescent="0.45">
       <c r="C10" s="4" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="11" spans="3:11" ht="204" x14ac:dyDescent="0.45">
       <c r="C11" s="1" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="12" spans="3:11" ht="187" x14ac:dyDescent="0.45">
       <c r="C12" s="1" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
     </row>
     <row r="13" spans="3:11" ht="187" x14ac:dyDescent="0.45">
       <c r="C13" s="1" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="14" spans="3:11" ht="187" x14ac:dyDescent="0.45">
       <c r="C14" s="1" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="15" spans="3:11" ht="68" x14ac:dyDescent="0.45">
       <c r="C15" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>378</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>379</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>380</v>
       </c>
       <c r="K15">
         <v>1</v>
@@ -6855,13 +6855,13 @@
     </row>
     <row r="16" spans="3:11" ht="68" x14ac:dyDescent="0.45">
       <c r="C16" s="1" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="K16">
         <v>2</v>
@@ -6869,13 +6869,13 @@
     </row>
     <row r="17" spans="3:11" ht="68" x14ac:dyDescent="0.45">
       <c r="C17" s="1" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="K17">
         <v>2</v>
@@ -6883,13 +6883,13 @@
     </row>
     <row r="18" spans="3:11" ht="85" x14ac:dyDescent="0.45">
       <c r="C18" s="1" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="K18">
         <v>2</v>
@@ -6897,13 +6897,13 @@
     </row>
     <row r="19" spans="3:11" ht="68" x14ac:dyDescent="0.45">
       <c r="C19" s="1" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="K19">
         <v>2</v>
@@ -6911,33 +6911,33 @@
     </row>
     <row r="22" spans="3:11" x14ac:dyDescent="0.45">
       <c r="C22" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="23" spans="3:11" ht="34" x14ac:dyDescent="0.45">
       <c r="C23" s="1" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="24" spans="3:11" ht="68" x14ac:dyDescent="0.45">
       <c r="C24" s="1" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="25" spans="3:11" ht="85" x14ac:dyDescent="0.45">
       <c r="C25" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="26" spans="3:11" ht="51" x14ac:dyDescent="0.45">
       <c r="C26" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="E26" s="1" t="s">
         <v>391</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>392</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>393</v>
       </c>
       <c r="K26">
         <v>2</v>
@@ -6945,13 +6945,13 @@
     </row>
     <row r="27" spans="3:11" ht="51" x14ac:dyDescent="0.45">
       <c r="C27" s="1" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="K27">
         <v>2</v>
@@ -6959,13 +6959,13 @@
     </row>
     <row r="28" spans="3:11" ht="51" x14ac:dyDescent="0.45">
       <c r="C28" s="1" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="K28">
         <v>2</v>
@@ -6973,48 +6973,48 @@
     </row>
     <row r="31" spans="3:11" x14ac:dyDescent="0.45">
       <c r="C31" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="32" spans="3:11" ht="153" x14ac:dyDescent="0.45">
       <c r="C32" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
     </row>
     <row r="33" spans="3:11" ht="85" x14ac:dyDescent="0.45">
       <c r="C33" s="1" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="34" spans="3:11" ht="204" x14ac:dyDescent="0.45">
       <c r="C34" s="1" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="35" spans="3:11" ht="204" x14ac:dyDescent="0.45">
       <c r="C35" s="1" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="36" spans="3:11" ht="34" x14ac:dyDescent="0.45">
       <c r="C36" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
     </row>
     <row r="37" spans="3:11" ht="102" x14ac:dyDescent="0.45">
       <c r="C37" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="38" spans="3:11" ht="68" x14ac:dyDescent="0.45">
       <c r="C38" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="E38" s="1" t="s">
         <v>400</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>402</v>
       </c>
       <c r="K38">
         <v>1</v>
@@ -7022,13 +7022,13 @@
     </row>
     <row r="39" spans="3:11" ht="51" x14ac:dyDescent="0.45">
       <c r="C39" s="1" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="K39">
         <v>2</v>
@@ -7036,13 +7036,13 @@
     </row>
     <row r="40" spans="3:11" ht="85" x14ac:dyDescent="0.45">
       <c r="C40" s="1" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="K40">
         <v>2</v>
@@ -7050,13 +7050,13 @@
     </row>
     <row r="41" spans="3:11" ht="51" x14ac:dyDescent="0.45">
       <c r="C41" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="K41">
         <v>2</v>
@@ -7064,13 +7064,13 @@
     </row>
     <row r="42" spans="3:11" ht="51" x14ac:dyDescent="0.45">
       <c r="C42" s="1" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="K42">
         <v>2</v>
@@ -7078,13 +7078,13 @@
     </row>
     <row r="43" spans="3:11" ht="51" x14ac:dyDescent="0.45">
       <c r="C43" s="1" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="K43">
         <v>2</v>
@@ -7092,13 +7092,13 @@
     </row>
     <row r="44" spans="3:11" ht="68" x14ac:dyDescent="0.45">
       <c r="C44" s="1" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="K44">
         <v>1</v>
@@ -7106,13 +7106,13 @@
     </row>
     <row r="45" spans="3:11" ht="34" x14ac:dyDescent="0.45">
       <c r="C45" s="1" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="K45">
         <v>2</v>
@@ -7120,13 +7120,13 @@
     </row>
     <row r="46" spans="3:11" ht="34" x14ac:dyDescent="0.45">
       <c r="C46" s="1" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="K46">
         <v>2</v>
@@ -7134,13 +7134,13 @@
     </row>
     <row r="47" spans="3:11" ht="51" x14ac:dyDescent="0.45">
       <c r="C47" s="1" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="K47">
         <v>2</v>
@@ -7148,13 +7148,13 @@
     </row>
     <row r="48" spans="3:11" ht="34" x14ac:dyDescent="0.45">
       <c r="C48" s="1" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="K48">
         <v>2</v>
@@ -7162,13 +7162,13 @@
     </row>
     <row r="49" spans="3:11" ht="34" x14ac:dyDescent="0.45">
       <c r="C49" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="K49">
         <v>2</v>
@@ -7176,13 +7176,13 @@
     </row>
     <row r="50" spans="3:11" ht="34" x14ac:dyDescent="0.45">
       <c r="C50" s="1" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="K50">
         <v>1</v>
@@ -7190,13 +7190,13 @@
     </row>
     <row r="51" spans="3:11" ht="51" x14ac:dyDescent="0.45">
       <c r="C51" s="1" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="K51">
         <v>2</v>
@@ -7204,13 +7204,13 @@
     </row>
     <row r="52" spans="3:11" ht="34" x14ac:dyDescent="0.45">
       <c r="C52" s="1" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="K52">
         <v>1</v>
@@ -7218,13 +7218,13 @@
     </row>
     <row r="53" spans="3:11" ht="102" x14ac:dyDescent="0.45">
       <c r="C53" s="1" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="K53">
         <v>1</v>
@@ -7232,13 +7232,13 @@
     </row>
     <row r="54" spans="3:11" ht="34" x14ac:dyDescent="0.45">
       <c r="C54" s="1" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="K54">
         <v>1</v>
@@ -7246,13 +7246,13 @@
     </row>
     <row r="55" spans="3:11" ht="68" x14ac:dyDescent="0.45">
       <c r="C55" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="K55">
         <v>2</v>
@@ -7260,13 +7260,13 @@
     </row>
     <row r="56" spans="3:11" ht="102" x14ac:dyDescent="0.45">
       <c r="C56" s="1" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="K56">
         <v>1</v>
@@ -7274,13 +7274,13 @@
     </row>
     <row r="57" spans="3:11" ht="51" x14ac:dyDescent="0.45">
       <c r="C57" s="1" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="K57">
         <v>2</v>
@@ -7288,13 +7288,13 @@
     </row>
     <row r="58" spans="3:11" ht="102" x14ac:dyDescent="0.45">
       <c r="C58" s="1" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="D58" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E58" s="1" t="s">
         <v>119</v>
-      </c>
-      <c r="E58" s="1" t="s">
-        <v>120</v>
       </c>
       <c r="K58">
         <v>2</v>
@@ -7302,28 +7302,28 @@
     </row>
     <row r="61" spans="3:11" x14ac:dyDescent="0.45">
       <c r="C61" s="2" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="62" spans="3:11" ht="51" x14ac:dyDescent="0.45">
       <c r="C62" s="4" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="63" spans="3:11" x14ac:dyDescent="0.45">
       <c r="C63" s="4" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="64" spans="3:11" ht="34" x14ac:dyDescent="0.45">
       <c r="C64" s="1" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="K64">
         <v>2</v>
@@ -7331,13 +7331,13 @@
     </row>
     <row r="65" spans="3:11" ht="34" x14ac:dyDescent="0.45">
       <c r="C65" s="1" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="K65">
         <v>1</v>
@@ -7345,13 +7345,13 @@
     </row>
     <row r="66" spans="3:11" ht="102" x14ac:dyDescent="0.45">
       <c r="C66" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="E66" s="1" t="s">
         <v>430</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="E66" s="1" t="s">
-        <v>432</v>
       </c>
       <c r="K66">
         <v>2</v>
@@ -7359,18 +7359,18 @@
     </row>
     <row r="69" spans="3:11" x14ac:dyDescent="0.45">
       <c r="C69" s="2" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="70" spans="3:11" ht="34" x14ac:dyDescent="0.45">
       <c r="C70" s="1" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="K70">
         <v>1</v>
@@ -7378,13 +7378,13 @@
     </row>
     <row r="71" spans="3:11" x14ac:dyDescent="0.45">
       <c r="C71" s="1" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="K71">
         <v>1</v>
@@ -7395,33 +7395,33 @@
     </row>
     <row r="73" spans="3:11" x14ac:dyDescent="0.45">
       <c r="C73" s="2" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="74" spans="3:11" ht="68" x14ac:dyDescent="0.45">
       <c r="C74" s="1" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="75" spans="3:11" ht="51" x14ac:dyDescent="0.45">
       <c r="C75" s="1" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
     </row>
     <row r="76" spans="3:11" ht="187" x14ac:dyDescent="0.45">
       <c r="C76" s="1" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
     </row>
     <row r="77" spans="3:11" ht="34" x14ac:dyDescent="0.45">
       <c r="C77" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="E77" s="1" t="s">
         <v>442</v>
-      </c>
-      <c r="D77" s="1" t="s">
-        <v>443</v>
-      </c>
-      <c r="E77" s="1" t="s">
-        <v>444</v>
       </c>
       <c r="K77">
         <v>1</v>
@@ -7429,13 +7429,13 @@
     </row>
     <row r="78" spans="3:11" ht="34" x14ac:dyDescent="0.45">
       <c r="C78" s="1" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="K78">
         <v>1</v>
@@ -7443,13 +7443,13 @@
     </row>
     <row r="79" spans="3:11" ht="34" x14ac:dyDescent="0.45">
       <c r="C79" s="1" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="K79">
         <v>2</v>
@@ -7457,13 +7457,13 @@
     </row>
     <row r="80" spans="3:11" ht="51" x14ac:dyDescent="0.45">
       <c r="C80" s="1" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="K80">
         <v>1</v>
@@ -7471,13 +7471,13 @@
     </row>
     <row r="81" spans="3:11" ht="34" x14ac:dyDescent="0.45">
       <c r="C81" s="1" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="K81">
         <v>2</v>
@@ -7485,33 +7485,33 @@
     </row>
     <row r="84" spans="3:11" x14ac:dyDescent="0.45">
       <c r="C84" s="2" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
     <row r="85" spans="3:11" ht="68" x14ac:dyDescent="0.45">
       <c r="C85" s="4" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="86" spans="3:11" ht="51" x14ac:dyDescent="0.45">
       <c r="C86" s="4" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="87" spans="3:11" ht="85" x14ac:dyDescent="0.45">
       <c r="C87" s="4" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
     </row>
     <row r="88" spans="3:11" ht="51" x14ac:dyDescent="0.45">
       <c r="C88" s="4" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="K88">
         <v>2</v>
@@ -7519,13 +7519,13 @@
     </row>
     <row r="89" spans="3:11" ht="51" x14ac:dyDescent="0.45">
       <c r="C89" s="1" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="K89">
         <v>1</v>
@@ -7533,13 +7533,13 @@
     </row>
     <row r="90" spans="3:11" ht="34" x14ac:dyDescent="0.45">
       <c r="C90" s="1" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="K90">
         <v>1</v>
@@ -7547,13 +7547,13 @@
     </row>
     <row r="91" spans="3:11" ht="68" x14ac:dyDescent="0.45">
       <c r="C91" s="1" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="K91">
         <v>2</v>
@@ -7561,13 +7561,13 @@
     </row>
     <row r="92" spans="3:11" ht="34" x14ac:dyDescent="0.45">
       <c r="C92" s="1" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="K92">
         <v>2</v>
@@ -7575,13 +7575,13 @@
     </row>
     <row r="93" spans="3:11" ht="68" x14ac:dyDescent="0.45">
       <c r="C93" s="1" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="K93">
         <v>1</v>
@@ -7589,13 +7589,13 @@
     </row>
     <row r="94" spans="3:11" ht="51" x14ac:dyDescent="0.45">
       <c r="C94" s="1" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="K94">
         <v>2</v>
@@ -7603,13 +7603,13 @@
     </row>
     <row r="95" spans="3:11" ht="51" x14ac:dyDescent="0.45">
       <c r="C95" s="1" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="K95">
         <v>1</v>
@@ -7617,28 +7617,28 @@
     </row>
     <row r="98" spans="3:11" x14ac:dyDescent="0.45">
       <c r="C98" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
     <row r="99" spans="3:11" ht="102" x14ac:dyDescent="0.45">
       <c r="C99" s="4" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="100" spans="3:11" ht="102" x14ac:dyDescent="0.45">
       <c r="C100" s="4" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
     </row>
     <row r="101" spans="3:11" ht="34" x14ac:dyDescent="0.45">
       <c r="C101" s="1" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="K101">
         <v>1</v>
@@ -7646,13 +7646,13 @@
     </row>
     <row r="102" spans="3:11" ht="34" x14ac:dyDescent="0.45">
       <c r="C102" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="E102" s="1" t="s">
         <v>469</v>
-      </c>
-      <c r="D102" s="1" t="s">
-        <v>470</v>
-      </c>
-      <c r="E102" s="1" t="s">
-        <v>471</v>
       </c>
       <c r="K102">
         <v>1</v>
@@ -7660,13 +7660,13 @@
     </row>
     <row r="103" spans="3:11" ht="51" x14ac:dyDescent="0.45">
       <c r="C103" s="1" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="K103">
         <v>2</v>
@@ -7674,13 +7674,13 @@
     </row>
     <row r="104" spans="3:11" ht="34" x14ac:dyDescent="0.45">
       <c r="C104" s="1" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="K104">
         <v>1</v>
@@ -7688,13 +7688,13 @@
     </row>
     <row r="105" spans="3:11" ht="34" x14ac:dyDescent="0.45">
       <c r="C105" s="1" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="K105">
         <v>2</v>
@@ -7702,13 +7702,13 @@
     </row>
     <row r="106" spans="3:11" ht="34" x14ac:dyDescent="0.45">
       <c r="C106" s="1" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="K106">
         <v>2</v>
@@ -7716,13 +7716,13 @@
     </row>
     <row r="107" spans="3:11" x14ac:dyDescent="0.45">
       <c r="C107" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="D107" s="1" t="s">
         <v>477</v>
       </c>
-      <c r="D107" s="1" t="s">
-        <v>479</v>
-      </c>
       <c r="E107" s="1" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="K107">
         <v>1</v>
@@ -7730,13 +7730,13 @@
     </row>
     <row r="108" spans="3:11" x14ac:dyDescent="0.45">
       <c r="C108" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="E108" s="1" t="s">
         <v>478</v>
-      </c>
-      <c r="D108" s="1" t="s">
-        <v>479</v>
-      </c>
-      <c r="E108" s="1" t="s">
-        <v>480</v>
       </c>
       <c r="K108">
         <v>2</v>
@@ -7744,13 +7744,13 @@
     </row>
     <row r="109" spans="3:11" ht="34" x14ac:dyDescent="0.45">
       <c r="C109" s="1" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="K109">
         <v>2</v>
@@ -7758,13 +7758,13 @@
     </row>
     <row r="110" spans="3:11" ht="34" x14ac:dyDescent="0.45">
       <c r="C110" s="1" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="K110">
         <v>1</v>
@@ -7772,13 +7772,13 @@
     </row>
     <row r="111" spans="3:11" ht="68" x14ac:dyDescent="0.45">
       <c r="C111" s="1" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="K111">
         <v>2</v>

--- a/db/DB_수사종결까지.xlsx
+++ b/db/DB_수사종결까지.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\songjoo\Documents\GitHub\word-game\db\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D66877F8-1C33-48FB-8085-F28568F65329}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82AB4BBA-1230-48B2-91C9-FFE9C86E024E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="3" xr2:uid="{5A5E7394-FEFB-4E15-8D3D-4FA3946DC3B9}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{5A5E7394-FEFB-4E15-8D3D-4FA3946DC3B9}"/>
   </bookViews>
   <sheets>
     <sheet name="관할 및 제척기피" sheetId="1" r:id="rId1"/>
